--- a/output_boron/boron_Intermediate_greenop_2014.xlsx
+++ b/output_boron/boron_Intermediate_greenop_2014.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
   <si>
     <t>NA</t>
   </si>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1002/2014PA002653</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_greenop_2014.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_greenop_2014_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Holbourn, A et al. (2004): Middle Miocene isotope stratigraphy and paleoceanographic evolution of the northwest and southwest Australian margins (Wombat Plateau and Great Australian Bight). Palaeogeography, Palaeoclimatology, Palaeoecology, 208(1-2), 1-22,</t>
+    <t xml:space="preserve">Holbourn, A et al. (2004): Middle Miocene isotope stratigraphy and paleoceanographic evolution of the northwest and southwest Australian margins (Wombat Plateau and Great Australian Bight). Palaeogeography, Palaeoclimatology, Palaeoecology, 208(1-2), 1-22,</t>
   </si>
   <si>
     <t xml:space="preserve">T. trilobus</t>
@@ -1392,9 +1392,6 @@
   </si>
   <si>
     <t xml:space="preserve">MC-ICP-MS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">These CO2 estimates are updated in Sosdian et al. (2018). Note that air-sea disequilibrium in this study was acknowledged but not subtracted.</t>
   </si>
   <si>
     <t xml:space="preserve">761_B_6_3_118_120</t>
@@ -1504,7 +1501,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1564,12 +1561,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1683,7 +1674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1765,7 +1756,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2372,7 +2362,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2438,18 +2428,18 @@
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="s">
-        <v>250</v>
+      <c r="Y5" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2515,18 +2505,18 @@
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="s">
-        <v>250</v>
+      <c r="Y6" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2592,18 +2582,18 @@
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="s">
-        <v>250</v>
+      <c r="Y7" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2669,18 +2659,18 @@
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="s">
-        <v>250</v>
+      <c r="Y8" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2746,18 +2736,18 @@
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="s">
-        <v>250</v>
+      <c r="Y9" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2823,18 +2813,18 @@
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="s">
-        <v>250</v>
+      <c r="Y10" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2900,18 +2890,18 @@
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="s">
-        <v>250</v>
+      <c r="Y11" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2977,18 +2967,18 @@
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="s">
-        <v>250</v>
+      <c r="Y12" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3054,18 +3044,18 @@
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="s">
-        <v>250</v>
+      <c r="Y13" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3131,18 +3121,18 @@
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="s">
-        <v>250</v>
+      <c r="Y14" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3208,18 +3198,18 @@
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="s">
-        <v>250</v>
+      <c r="Y15" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3285,18 +3275,18 @@
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="s">
-        <v>250</v>
+      <c r="Y16" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3362,18 +3352,18 @@
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="s">
-        <v>250</v>
+      <c r="Y17" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3439,18 +3429,18 @@
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="s">
-        <v>250</v>
+      <c r="Y18" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3516,18 +3506,18 @@
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="s">
-        <v>250</v>
+      <c r="Y19" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3593,18 +3583,18 @@
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="s">
-        <v>250</v>
+      <c r="Y20" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3670,18 +3660,18 @@
       <c r="X21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y21" t="s">
-        <v>250</v>
+      <c r="Y21" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3747,18 +3737,18 @@
       <c r="X22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y22" t="s">
-        <v>250</v>
+      <c r="Y22" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3824,18 +3814,18 @@
       <c r="X23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y23" t="s">
-        <v>250</v>
+      <c r="Y23" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3901,18 +3891,18 @@
       <c r="X24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y24" t="s">
-        <v>250</v>
+      <c r="Y24" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -3978,18 +3968,18 @@
       <c r="X25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y25" t="s">
-        <v>250</v>
+      <c r="Y25" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4055,18 +4045,18 @@
       <c r="X26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y26" t="s">
-        <v>250</v>
+      <c r="Y26" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4132,18 +4122,18 @@
       <c r="X27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y27" t="s">
-        <v>250</v>
+      <c r="Y27" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4209,18 +4199,18 @@
       <c r="X28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y28" t="s">
-        <v>250</v>
+      <c r="Y28" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4286,18 +4276,18 @@
       <c r="X29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y29" t="s">
-        <v>250</v>
+      <c r="Y29" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4363,18 +4353,18 @@
       <c r="X30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y30" t="s">
-        <v>250</v>
+      <c r="Y30" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4440,18 +4430,18 @@
       <c r="X31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y31" t="s">
-        <v>250</v>
+      <c r="Y31" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4517,18 +4507,18 @@
       <c r="X32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y32" t="s">
-        <v>250</v>
+      <c r="Y32" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4594,18 +4584,18 @@
       <c r="X33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y33" t="s">
-        <v>250</v>
+      <c r="Y33" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4671,18 +4661,18 @@
       <c r="X34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y34" t="s">
-        <v>250</v>
+      <c r="Y34" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4748,18 +4738,18 @@
       <c r="X35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y35" t="s">
-        <v>250</v>
+      <c r="Y35" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -4825,18 +4815,18 @@
       <c r="X36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y36" t="s">
-        <v>250</v>
+      <c r="Y36" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -4902,18 +4892,18 @@
       <c r="X37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y37" t="s">
-        <v>250</v>
+      <c r="Y37" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -4929,7 +4919,7 @@
         <v>115.53611111</v>
       </c>
       <c r="H38" t="n">
-        <v>16.9752108641057</v>
+        <v>16.9752108641058</v>
       </c>
       <c r="I38" t="e">
         <v>#N/A</v>
@@ -4979,18 +4969,18 @@
       <c r="X38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y38" t="s">
-        <v>250</v>
+      <c r="Y38" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5056,8 +5046,8 @@
       <c r="X39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y39" t="s">
-        <v>250</v>
+      <c r="Y39" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -5267,43 +5257,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
